--- a/test-case-exports/ForgotPassword.xlsx
+++ b/test-case-exports/ForgotPassword.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1422" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1434" uniqueCount="229">
   <si>
     <t>#</t>
   </si>
@@ -131,9 +131,6 @@
     <t>No</t>
   </si>
   <si>
-    <t>route mocking</t>
-  </si>
-  <si>
     <t>should not redirect to login when reset is submitted with mismatched passwords</t>
   </si>
   <si>
@@ -296,7 +293,8 @@
     <t>Skipped</t>
   </si>
   <si>
-    <t>test.skip() on this test; route mocking</t>
+    <t xml:space="preserve">Skipped: async ({ page }) =&gt; {
+        await mockForgetPasswordSuccess(page</t>
   </si>
   <si>
     <t>should not send duplicate API requests when Next is double-clicked</t>
@@ -392,6 +390,10 @@
     <t>should preserve Company and Mobile number values when navigating back to step 1</t>
   </si>
   <si>
+    <t xml:space="preserve">Skipped: async () =&gt; {
+        await forgotPassword.backButton.click(</t>
+  </si>
+  <si>
     <t>Forgot Password — Step 2: Interactions</t>
   </si>
   <si>
@@ -671,13 +673,13 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-07-26T17:32:41.249Z</t>
+    <t>2026-09-08T15:08:53.362Z</t>
   </si>
   <si>
     <t>Total test cases</t>
   </si>
   <si>
-    <t>Count per sub-folder (ui / functional / api / archive)</t>
+    <t>Count per sub-folder</t>
   </si>
   <si>
     <t>api</t>
@@ -695,7 +697,10 @@
     <t>Archived</t>
   </si>
   <si>
-    <t>Spec files in this module</t>
+    <t>Gated behind an env flag</t>
+  </si>
+  <si>
+    <t>Spec files</t>
   </si>
 </sst>
 </file>
@@ -713,6 +718,7 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
       <b/>
@@ -722,7 +728,7 @@
       <b/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -732,11 +738,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -754,8 +755,12 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -1100,17 +1105,18 @@
   <dimension ref="A1:I176"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="60" customWidth="1"/>
-    <col min="4" max="4" width="54" customWidth="1"/>
-    <col min="5" max="5" width="17" customWidth="1"/>
-    <col min="6" max="6" width="60" customWidth="1"/>
-    <col min="7" max="8" width="15" customWidth="1"/>
-    <col min="9" max="9" width="41" customWidth="1"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="58" customWidth="1"/>
+    <col min="4" max="4" width="44" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="62" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
+    <col min="9" max="9" width="48" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1139,36 +1145,36 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2">
+    <row r="2" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="E2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1197,36 +1203,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4">
+    <row r="4" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="E4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1255,36 +1261,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6">
+    <row r="6" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="B6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="E6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1313,36 +1319,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8">
+    <row r="8" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="B8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="E8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1371,36 +1377,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" t="s">
+    <row r="10" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="E10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G10" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1429,36 +1435,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12">
+    <row r="12" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="B12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E12" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" t="s">
+      <c r="E12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="G12" t="s">
-        <v>14</v>
-      </c>
-      <c r="H12" t="s">
-        <v>15</v>
-      </c>
-      <c r="I12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1487,36 +1493,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14">
+    <row r="14" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="B14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="E14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G14" t="s">
-        <v>14</v>
-      </c>
-      <c r="H14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I14" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1545,36 +1551,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" t="s">
+    <row r="16" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E16" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="E16" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G16" t="s">
-        <v>14</v>
-      </c>
-      <c r="H16" t="s">
-        <v>15</v>
-      </c>
-      <c r="I16" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1603,36 +1609,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18">
+    <row r="18" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
         <v>17</v>
       </c>
-      <c r="B18" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="B18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E18" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18" t="s">
+      <c r="E18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G18" t="s">
-        <v>14</v>
-      </c>
-      <c r="H18" t="s">
-        <v>15</v>
-      </c>
-      <c r="I18" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1661,36 +1667,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20">
+    <row r="20" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
         <v>19</v>
       </c>
-      <c r="B20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="B20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E20" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" t="s">
+      <c r="E20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G20" t="s">
-        <v>14</v>
-      </c>
-      <c r="H20" t="s">
-        <v>15</v>
-      </c>
-      <c r="I20" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -1719,36 +1725,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22">
+    <row r="22" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
         <v>21</v>
       </c>
-      <c r="B22" t="s">
-        <v>9</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="B22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D22" t="s">
-        <v>12</v>
-      </c>
-      <c r="E22" t="s">
-        <v>12</v>
-      </c>
-      <c r="F22" t="s">
+      <c r="D22" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G22" t="s">
-        <v>14</v>
-      </c>
-      <c r="H22" t="s">
+      <c r="G22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H22" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I22" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I22" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -1765,7 +1771,7 @@
         <v>12</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>14</v>
@@ -1774,39 +1780,39 @@
         <v>38</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
         <v>23</v>
       </c>
-      <c r="B24" t="s">
-        <v>9</v>
-      </c>
-      <c r="C24" t="s">
+      <c r="B24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D24" t="s">
-        <v>12</v>
-      </c>
-      <c r="E24" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" t="s">
-        <v>41</v>
-      </c>
-      <c r="G24" t="s">
-        <v>14</v>
-      </c>
-      <c r="H24" t="s">
+      <c r="D24" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H24" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I24" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I24" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -1814,57 +1820,57 @@
         <v>9</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="E25" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F25" s="2" t="s">
+      <c r="G25" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G25" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>25</v>
-      </c>
-      <c r="B26" t="s">
-        <v>9</v>
-      </c>
-      <c r="C26" t="s">
-        <v>42</v>
-      </c>
-      <c r="D26" t="s">
-        <v>43</v>
-      </c>
-      <c r="E26" t="s">
-        <v>12</v>
-      </c>
-      <c r="F26" t="s">
-        <v>45</v>
-      </c>
-      <c r="G26" t="s">
-        <v>14</v>
-      </c>
-      <c r="H26" t="s">
-        <v>15</v>
-      </c>
-      <c r="I26" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G26" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -1872,57 +1878,57 @@
         <v>9</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="E27" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F27" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="G27" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>27</v>
-      </c>
-      <c r="B28" t="s">
-        <v>9</v>
-      </c>
-      <c r="C28" t="s">
-        <v>42</v>
-      </c>
-      <c r="D28" t="s">
-        <v>43</v>
-      </c>
-      <c r="E28" t="s">
-        <v>12</v>
-      </c>
-      <c r="F28" t="s">
-        <v>47</v>
-      </c>
-      <c r="G28" t="s">
-        <v>14</v>
-      </c>
-      <c r="H28" t="s">
-        <v>15</v>
-      </c>
-      <c r="I28" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G28" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -1930,57 +1936,57 @@
         <v>9</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="E29" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F29" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="G29" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>29</v>
-      </c>
-      <c r="B30" t="s">
-        <v>9</v>
-      </c>
-      <c r="C30" t="s">
-        <v>42</v>
-      </c>
-      <c r="D30" t="s">
-        <v>43</v>
-      </c>
-      <c r="E30" t="s">
-        <v>12</v>
-      </c>
-      <c r="F30" t="s">
-        <v>49</v>
-      </c>
-      <c r="G30" t="s">
-        <v>14</v>
-      </c>
-      <c r="H30" t="s">
-        <v>15</v>
-      </c>
-      <c r="I30" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G30" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -1988,57 +1994,57 @@
         <v>9</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="E31" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F31" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G31" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>31</v>
-      </c>
-      <c r="B32" t="s">
-        <v>9</v>
-      </c>
-      <c r="C32" t="s">
-        <v>42</v>
-      </c>
-      <c r="D32" t="s">
-        <v>43</v>
-      </c>
-      <c r="E32" t="s">
-        <v>12</v>
-      </c>
-      <c r="F32" t="s">
-        <v>51</v>
-      </c>
-      <c r="G32" t="s">
-        <v>14</v>
-      </c>
-      <c r="H32" t="s">
-        <v>15</v>
-      </c>
-      <c r="I32" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G32" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -2046,57 +2052,57 @@
         <v>9</v>
       </c>
       <c r="C33" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D33" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="E33" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F33" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="G33" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>33</v>
-      </c>
-      <c r="B34" t="s">
-        <v>9</v>
-      </c>
-      <c r="C34" t="s">
-        <v>42</v>
-      </c>
-      <c r="D34" t="s">
-        <v>43</v>
-      </c>
-      <c r="E34" t="s">
-        <v>12</v>
-      </c>
-      <c r="F34" t="s">
-        <v>53</v>
-      </c>
-      <c r="G34" t="s">
-        <v>14</v>
-      </c>
-      <c r="H34" t="s">
-        <v>15</v>
-      </c>
-      <c r="I34" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G34" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -2104,57 +2110,57 @@
         <v>9</v>
       </c>
       <c r="C35" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D35" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="E35" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F35" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F36" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="G35" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>35</v>
-      </c>
-      <c r="B36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C36" t="s">
-        <v>42</v>
-      </c>
-      <c r="D36" t="s">
-        <v>43</v>
-      </c>
-      <c r="E36" t="s">
-        <v>12</v>
-      </c>
-      <c r="F36" t="s">
-        <v>55</v>
-      </c>
-      <c r="G36" t="s">
-        <v>14</v>
-      </c>
-      <c r="H36" t="s">
-        <v>15</v>
-      </c>
-      <c r="I36" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G36" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -2162,57 +2168,57 @@
         <v>9</v>
       </c>
       <c r="C37" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D37" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D37" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="E37" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F37" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="G37" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I37" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>37</v>
-      </c>
-      <c r="B38" t="s">
-        <v>9</v>
-      </c>
-      <c r="C38" t="s">
+      <c r="D38" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D38" t="s">
+      <c r="E38" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F38" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E38" t="s">
-        <v>12</v>
-      </c>
-      <c r="F38" t="s">
-        <v>59</v>
-      </c>
-      <c r="G38" t="s">
-        <v>14</v>
-      </c>
-      <c r="H38" t="s">
-        <v>15</v>
-      </c>
-      <c r="I38" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G38" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -2220,57 +2226,57 @@
         <v>9</v>
       </c>
       <c r="C39" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D39" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="E39" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F39" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F40" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="G39" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I39" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>39</v>
-      </c>
-      <c r="B40" t="s">
-        <v>9</v>
-      </c>
-      <c r="C40" t="s">
-        <v>57</v>
-      </c>
-      <c r="D40" t="s">
-        <v>58</v>
-      </c>
-      <c r="E40" t="s">
-        <v>12</v>
-      </c>
-      <c r="F40" t="s">
-        <v>61</v>
-      </c>
-      <c r="G40" t="s">
-        <v>14</v>
-      </c>
-      <c r="H40" t="s">
-        <v>15</v>
-      </c>
-      <c r="I40" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G40" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -2278,57 +2284,57 @@
         <v>9</v>
       </c>
       <c r="C41" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D41" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D41" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="E41" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F41" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F42" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="G41" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>41</v>
-      </c>
-      <c r="B42" t="s">
-        <v>9</v>
-      </c>
-      <c r="C42" t="s">
-        <v>57</v>
-      </c>
-      <c r="D42" t="s">
-        <v>58</v>
-      </c>
-      <c r="E42" t="s">
-        <v>12</v>
-      </c>
-      <c r="F42" t="s">
-        <v>63</v>
-      </c>
-      <c r="G42" t="s">
-        <v>14</v>
-      </c>
-      <c r="H42" t="s">
-        <v>15</v>
-      </c>
-      <c r="I42" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G42" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -2336,57 +2342,57 @@
         <v>9</v>
       </c>
       <c r="C43" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D43" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D43" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="E43" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F43" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F44" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="G43" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I43" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <v>43</v>
-      </c>
-      <c r="B44" t="s">
-        <v>9</v>
-      </c>
-      <c r="C44" t="s">
-        <v>57</v>
-      </c>
-      <c r="D44" t="s">
-        <v>58</v>
-      </c>
-      <c r="E44" t="s">
-        <v>12</v>
-      </c>
-      <c r="F44" t="s">
-        <v>65</v>
-      </c>
-      <c r="G44" t="s">
-        <v>14</v>
-      </c>
-      <c r="H44" t="s">
-        <v>15</v>
-      </c>
-      <c r="I44" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G44" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>44</v>
       </c>
@@ -2394,57 +2400,57 @@
         <v>9</v>
       </c>
       <c r="C45" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D45" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D45" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="E45" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F45" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="2">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F46" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="G45" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I45" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46">
-        <v>45</v>
-      </c>
-      <c r="B46" t="s">
-        <v>9</v>
-      </c>
-      <c r="C46" t="s">
-        <v>57</v>
-      </c>
-      <c r="D46" t="s">
-        <v>58</v>
-      </c>
-      <c r="E46" t="s">
-        <v>12</v>
-      </c>
-      <c r="F46" t="s">
-        <v>67</v>
-      </c>
-      <c r="G46" t="s">
-        <v>14</v>
-      </c>
-      <c r="H46" t="s">
-        <v>15</v>
-      </c>
-      <c r="I46" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G46" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>46</v>
       </c>
@@ -2452,57 +2458,57 @@
         <v>9</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D47" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F47" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E47" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F47" s="2" t="s">
+      <c r="G47" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="2">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F48" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="G47" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H47" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I47" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48">
-        <v>47</v>
-      </c>
-      <c r="B48" t="s">
-        <v>9</v>
-      </c>
-      <c r="C48" t="s">
-        <v>57</v>
-      </c>
-      <c r="D48" t="s">
-        <v>68</v>
-      </c>
-      <c r="E48" t="s">
-        <v>12</v>
-      </c>
-      <c r="F48" t="s">
-        <v>70</v>
-      </c>
-      <c r="G48" t="s">
-        <v>14</v>
-      </c>
-      <c r="H48" t="s">
-        <v>15</v>
-      </c>
-      <c r="I48" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G48" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>48</v>
       </c>
@@ -2510,57 +2516,57 @@
         <v>9</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F49" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="2">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F50" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="G49" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H49" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I49" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50" t="s">
-        <v>9</v>
-      </c>
-      <c r="C50" t="s">
-        <v>57</v>
-      </c>
-      <c r="D50" t="s">
-        <v>68</v>
-      </c>
-      <c r="E50" t="s">
-        <v>12</v>
-      </c>
-      <c r="F50" t="s">
-        <v>72</v>
-      </c>
-      <c r="G50" t="s">
-        <v>14</v>
-      </c>
-      <c r="H50" t="s">
-        <v>15</v>
-      </c>
-      <c r="I50" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G50" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -2568,57 +2574,57 @@
         <v>9</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F51" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="2">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D52" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="G51" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I51" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="s">
-        <v>9</v>
-      </c>
-      <c r="C52" t="s">
-        <v>57</v>
-      </c>
-      <c r="D52" t="s">
+      <c r="E52" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F52" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E52" t="s">
-        <v>12</v>
-      </c>
-      <c r="F52" t="s">
-        <v>75</v>
-      </c>
-      <c r="G52" t="s">
-        <v>14</v>
-      </c>
-      <c r="H52" t="s">
-        <v>15</v>
-      </c>
-      <c r="I52" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G52" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>52</v>
       </c>
@@ -2626,57 +2632,57 @@
         <v>9</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F53" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="2">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F54" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="G53" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I53" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="s">
-        <v>9</v>
-      </c>
-      <c r="C54" t="s">
-        <v>57</v>
-      </c>
-      <c r="D54" t="s">
-        <v>74</v>
-      </c>
-      <c r="E54" t="s">
-        <v>12</v>
-      </c>
-      <c r="F54" t="s">
-        <v>77</v>
-      </c>
-      <c r="G54" t="s">
-        <v>14</v>
-      </c>
-      <c r="H54" t="s">
-        <v>15</v>
-      </c>
-      <c r="I54" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G54" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>54</v>
       </c>
@@ -2684,57 +2690,57 @@
         <v>9</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F55" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="2">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F56" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="G55" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H55" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I55" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" t="s">
-        <v>9</v>
-      </c>
-      <c r="C56" t="s">
-        <v>57</v>
-      </c>
-      <c r="D56" t="s">
-        <v>74</v>
-      </c>
-      <c r="E56" t="s">
-        <v>12</v>
-      </c>
-      <c r="F56" t="s">
-        <v>79</v>
-      </c>
-      <c r="G56" t="s">
-        <v>14</v>
-      </c>
-      <c r="H56" t="s">
-        <v>15</v>
-      </c>
-      <c r="I56" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G56" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>56</v>
       </c>
@@ -2742,57 +2748,57 @@
         <v>9</v>
       </c>
       <c r="C57" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="2">
         <v>57</v>
       </c>
-      <c r="D57" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F57" s="2" t="s">
+      <c r="B58" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F58" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="G57" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H57" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I57" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A58">
-        <v>57</v>
-      </c>
-      <c r="B58" t="s">
-        <v>9</v>
-      </c>
-      <c r="C58" t="s">
-        <v>57</v>
-      </c>
-      <c r="D58" t="s">
-        <v>74</v>
-      </c>
-      <c r="E58" t="s">
-        <v>12</v>
-      </c>
-      <c r="F58" t="s">
-        <v>81</v>
-      </c>
-      <c r="G58" t="s">
-        <v>14</v>
-      </c>
-      <c r="H58" t="s">
-        <v>15</v>
-      </c>
-      <c r="I58" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G58" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>58</v>
       </c>
@@ -2800,57 +2806,57 @@
         <v>9</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F59" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="2">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F60" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="G59" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H59" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I59" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60">
-        <v>59</v>
-      </c>
-      <c r="B60" t="s">
-        <v>9</v>
-      </c>
-      <c r="C60" t="s">
-        <v>57</v>
-      </c>
-      <c r="D60" t="s">
-        <v>74</v>
-      </c>
-      <c r="E60" t="s">
-        <v>12</v>
-      </c>
-      <c r="F60" t="s">
-        <v>83</v>
-      </c>
-      <c r="G60" t="s">
-        <v>14</v>
-      </c>
-      <c r="H60" t="s">
-        <v>15</v>
-      </c>
-      <c r="I60" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G60" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>60</v>
       </c>
@@ -2858,57 +2864,57 @@
         <v>9</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F61" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="2">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F62" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="G61" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H61" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I61" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A62">
-        <v>61</v>
-      </c>
-      <c r="B62" t="s">
-        <v>9</v>
-      </c>
-      <c r="C62" t="s">
-        <v>57</v>
-      </c>
-      <c r="D62" t="s">
-        <v>74</v>
-      </c>
-      <c r="E62" t="s">
-        <v>12</v>
-      </c>
-      <c r="F62" t="s">
-        <v>85</v>
-      </c>
-      <c r="G62" t="s">
-        <v>14</v>
-      </c>
-      <c r="H62" t="s">
-        <v>15</v>
-      </c>
-      <c r="I62" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G62" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>62</v>
       </c>
@@ -2916,57 +2922,57 @@
         <v>9</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D63" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F63" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="E63" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F63" s="2" t="s">
+      <c r="G63" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="2">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F64" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="G63" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H63" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I63" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A64">
-        <v>63</v>
-      </c>
-      <c r="B64" t="s">
-        <v>9</v>
-      </c>
-      <c r="C64" t="s">
-        <v>57</v>
-      </c>
-      <c r="D64" t="s">
-        <v>86</v>
-      </c>
-      <c r="E64" t="s">
-        <v>12</v>
-      </c>
-      <c r="F64" t="s">
-        <v>88</v>
-      </c>
-      <c r="G64" t="s">
-        <v>14</v>
-      </c>
-      <c r="H64" t="s">
-        <v>15</v>
-      </c>
-      <c r="I64" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G64" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>64</v>
       </c>
@@ -2974,57 +2980,57 @@
         <v>9</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F65" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="2">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F66" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="G65" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H65" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I65" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A66">
-        <v>65</v>
-      </c>
-      <c r="B66" t="s">
-        <v>9</v>
-      </c>
-      <c r="C66" t="s">
-        <v>57</v>
-      </c>
-      <c r="D66" t="s">
-        <v>86</v>
-      </c>
-      <c r="E66" t="s">
-        <v>12</v>
-      </c>
-      <c r="F66" t="s">
-        <v>90</v>
-      </c>
-      <c r="G66" t="s">
-        <v>14</v>
-      </c>
-      <c r="H66" t="s">
-        <v>15</v>
-      </c>
-      <c r="I66" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G66" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>66</v>
       </c>
@@ -3032,57 +3038,57 @@
         <v>9</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F67" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="2">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F68" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="G67" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H67" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I67" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A68">
-        <v>67</v>
-      </c>
-      <c r="B68" t="s">
-        <v>9</v>
-      </c>
-      <c r="C68" t="s">
-        <v>57</v>
-      </c>
-      <c r="D68" t="s">
-        <v>86</v>
-      </c>
-      <c r="E68" t="s">
-        <v>12</v>
-      </c>
-      <c r="F68" t="s">
+      <c r="G68" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="G68" t="s">
+      <c r="H68" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I68" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="H68" t="s">
-        <v>15</v>
-      </c>
-      <c r="I68" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="69" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>68</v>
       </c>
@@ -3090,57 +3096,57 @@
         <v>9</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F69" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="2">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F70" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="G69" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H69" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I69" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A70">
-        <v>69</v>
-      </c>
-      <c r="B70" t="s">
-        <v>9</v>
-      </c>
-      <c r="C70" t="s">
-        <v>57</v>
-      </c>
-      <c r="D70" t="s">
-        <v>86</v>
-      </c>
-      <c r="E70" t="s">
-        <v>12</v>
-      </c>
-      <c r="F70" t="s">
-        <v>96</v>
-      </c>
-      <c r="G70" t="s">
-        <v>14</v>
-      </c>
-      <c r="H70" t="s">
-        <v>15</v>
-      </c>
-      <c r="I70" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G70" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>70</v>
       </c>
@@ -3148,57 +3154,57 @@
         <v>9</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F71" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="2">
+        <v>71</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D72" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="G71" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H71" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I71" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A72">
-        <v>71</v>
-      </c>
-      <c r="B72" t="s">
-        <v>9</v>
-      </c>
-      <c r="C72" t="s">
-        <v>57</v>
-      </c>
-      <c r="D72" t="s">
+      <c r="E72" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F72" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E72" t="s">
-        <v>12</v>
-      </c>
-      <c r="F72" t="s">
-        <v>99</v>
-      </c>
-      <c r="G72" t="s">
-        <v>14</v>
-      </c>
-      <c r="H72" t="s">
-        <v>15</v>
-      </c>
-      <c r="I72" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G72" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>72</v>
       </c>
@@ -3206,57 +3212,57 @@
         <v>9</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F73" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="2">
+        <v>73</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F74" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="G73" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H73" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I73" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A74">
-        <v>73</v>
-      </c>
-      <c r="B74" t="s">
-        <v>9</v>
-      </c>
-      <c r="C74" t="s">
-        <v>57</v>
-      </c>
-      <c r="D74" t="s">
-        <v>98</v>
-      </c>
-      <c r="E74" t="s">
-        <v>12</v>
-      </c>
-      <c r="F74" t="s">
-        <v>101</v>
-      </c>
-      <c r="G74" t="s">
-        <v>14</v>
-      </c>
-      <c r="H74" t="s">
-        <v>15</v>
-      </c>
-      <c r="I74" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G74" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>74</v>
       </c>
@@ -3264,57 +3270,57 @@
         <v>9</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F75" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I75" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="2">
+        <v>75</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F76" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="G75" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H75" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I75" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A76">
-        <v>75</v>
-      </c>
-      <c r="B76" t="s">
-        <v>9</v>
-      </c>
-      <c r="C76" t="s">
-        <v>57</v>
-      </c>
-      <c r="D76" t="s">
-        <v>98</v>
-      </c>
-      <c r="E76" t="s">
-        <v>12</v>
-      </c>
-      <c r="F76" t="s">
-        <v>103</v>
-      </c>
-      <c r="G76" t="s">
-        <v>14</v>
-      </c>
-      <c r="H76" t="s">
-        <v>15</v>
-      </c>
-      <c r="I76" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G76" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>76</v>
       </c>
@@ -3322,57 +3328,57 @@
         <v>9</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F77" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="2">
+        <v>77</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F78" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="G77" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H77" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I77" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A78">
-        <v>77</v>
-      </c>
-      <c r="B78" t="s">
-        <v>9</v>
-      </c>
-      <c r="C78" t="s">
-        <v>57</v>
-      </c>
-      <c r="D78" t="s">
-        <v>98</v>
-      </c>
-      <c r="E78" t="s">
-        <v>12</v>
-      </c>
-      <c r="F78" t="s">
-        <v>105</v>
-      </c>
-      <c r="G78" t="s">
-        <v>14</v>
-      </c>
-      <c r="H78" t="s">
-        <v>15</v>
-      </c>
-      <c r="I78" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G78" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>78</v>
       </c>
@@ -3380,57 +3386,57 @@
         <v>9</v>
       </c>
       <c r="C79" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D79" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D79" s="2" t="s">
+      <c r="E79" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F79" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="E79" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F79" s="2" t="s">
+      <c r="G79" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="2">
+        <v>79</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F80" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="G79" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H79" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I79" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A80">
-        <v>79</v>
-      </c>
-      <c r="B80" t="s">
-        <v>9</v>
-      </c>
-      <c r="C80" t="s">
-        <v>106</v>
-      </c>
-      <c r="D80" t="s">
-        <v>107</v>
-      </c>
-      <c r="E80" t="s">
-        <v>12</v>
-      </c>
-      <c r="F80" t="s">
-        <v>109</v>
-      </c>
-      <c r="G80" t="s">
-        <v>14</v>
-      </c>
-      <c r="H80" t="s">
-        <v>15</v>
-      </c>
-      <c r="I80" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G80" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>80</v>
       </c>
@@ -3438,57 +3444,57 @@
         <v>9</v>
       </c>
       <c r="C81" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D81" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D81" s="2" t="s">
-        <v>107</v>
-      </c>
       <c r="E81" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F81" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I81" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="2">
+        <v>81</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F82" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="G81" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H81" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I81" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A82">
-        <v>81</v>
-      </c>
-      <c r="B82" t="s">
-        <v>9</v>
-      </c>
-      <c r="C82" t="s">
-        <v>106</v>
-      </c>
-      <c r="D82" t="s">
-        <v>107</v>
-      </c>
-      <c r="E82" t="s">
-        <v>12</v>
-      </c>
-      <c r="F82" t="s">
-        <v>111</v>
-      </c>
-      <c r="G82" t="s">
-        <v>14</v>
-      </c>
-      <c r="H82" t="s">
-        <v>15</v>
-      </c>
-      <c r="I82" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G82" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>82</v>
       </c>
@@ -3496,57 +3502,57 @@
         <v>9</v>
       </c>
       <c r="C83" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D83" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D83" s="2" t="s">
-        <v>107</v>
-      </c>
       <c r="E83" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F83" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I83" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="2">
+        <v>83</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F84" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="G83" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H83" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I83" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A84">
-        <v>83</v>
-      </c>
-      <c r="B84" t="s">
-        <v>9</v>
-      </c>
-      <c r="C84" t="s">
-        <v>106</v>
-      </c>
-      <c r="D84" t="s">
-        <v>107</v>
-      </c>
-      <c r="E84" t="s">
-        <v>12</v>
-      </c>
-      <c r="F84" t="s">
-        <v>113</v>
-      </c>
-      <c r="G84" t="s">
-        <v>14</v>
-      </c>
-      <c r="H84" t="s">
-        <v>15</v>
-      </c>
-      <c r="I84" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G84" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>84</v>
       </c>
@@ -3554,57 +3560,57 @@
         <v>9</v>
       </c>
       <c r="C85" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D85" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D85" s="2" t="s">
-        <v>107</v>
-      </c>
       <c r="E85" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F85" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I85" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="2">
+        <v>85</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F86" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="G85" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H85" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I85" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A86">
-        <v>85</v>
-      </c>
-      <c r="B86" t="s">
-        <v>9</v>
-      </c>
-      <c r="C86" t="s">
-        <v>106</v>
-      </c>
-      <c r="D86" t="s">
-        <v>107</v>
-      </c>
-      <c r="E86" t="s">
-        <v>12</v>
-      </c>
-      <c r="F86" t="s">
-        <v>115</v>
-      </c>
-      <c r="G86" t="s">
-        <v>14</v>
-      </c>
-      <c r="H86" t="s">
-        <v>15</v>
-      </c>
-      <c r="I86" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G86" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>86</v>
       </c>
@@ -3612,57 +3618,57 @@
         <v>9</v>
       </c>
       <c r="C87" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D87" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D87" s="2" t="s">
-        <v>107</v>
-      </c>
       <c r="E87" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F87" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I87" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="2">
+        <v>87</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F88" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="G87" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H87" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I87" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A88">
-        <v>87</v>
-      </c>
-      <c r="B88" t="s">
-        <v>9</v>
-      </c>
-      <c r="C88" t="s">
-        <v>106</v>
-      </c>
-      <c r="D88" t="s">
-        <v>107</v>
-      </c>
-      <c r="E88" t="s">
-        <v>12</v>
-      </c>
-      <c r="F88" t="s">
-        <v>117</v>
-      </c>
-      <c r="G88" t="s">
-        <v>14</v>
-      </c>
-      <c r="H88" t="s">
-        <v>15</v>
-      </c>
-      <c r="I88" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G88" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I88" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>88</v>
       </c>
@@ -3670,57 +3676,57 @@
         <v>9</v>
       </c>
       <c r="C89" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D89" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D89" s="2" t="s">
-        <v>107</v>
-      </c>
       <c r="E89" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F89" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I89" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="2">
+        <v>89</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F90" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="G89" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H89" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I89" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A90">
-        <v>89</v>
-      </c>
-      <c r="B90" t="s">
-        <v>9</v>
-      </c>
-      <c r="C90" t="s">
-        <v>106</v>
-      </c>
-      <c r="D90" t="s">
-        <v>107</v>
-      </c>
-      <c r="E90" t="s">
-        <v>12</v>
-      </c>
-      <c r="F90" t="s">
-        <v>119</v>
-      </c>
-      <c r="G90" t="s">
-        <v>14</v>
-      </c>
-      <c r="H90" t="s">
-        <v>15</v>
-      </c>
-      <c r="I90" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G90" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I90" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>90</v>
       </c>
@@ -3728,57 +3734,57 @@
         <v>9</v>
       </c>
       <c r="C91" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D91" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D91" s="2" t="s">
-        <v>107</v>
-      </c>
       <c r="E91" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F91" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I91" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="2">
+        <v>91</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D92" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="G91" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H91" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I91" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A92">
-        <v>91</v>
-      </c>
-      <c r="B92" t="s">
-        <v>9</v>
-      </c>
-      <c r="C92" t="s">
-        <v>106</v>
-      </c>
-      <c r="D92" t="s">
+      <c r="E92" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F92" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="E92" t="s">
-        <v>12</v>
-      </c>
-      <c r="F92" t="s">
-        <v>122</v>
-      </c>
-      <c r="G92" t="s">
-        <v>14</v>
-      </c>
-      <c r="H92" t="s">
-        <v>15</v>
-      </c>
-      <c r="I92" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G92" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I92" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
         <v>92</v>
       </c>
@@ -3786,57 +3792,57 @@
         <v>9</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F93" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I93" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="2">
+        <v>93</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F94" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="G93" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H93" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I93" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A94">
-        <v>93</v>
-      </c>
-      <c r="B94" t="s">
-        <v>9</v>
-      </c>
-      <c r="C94" t="s">
-        <v>106</v>
-      </c>
-      <c r="D94" t="s">
-        <v>121</v>
-      </c>
-      <c r="E94" t="s">
-        <v>12</v>
-      </c>
-      <c r="F94" t="s">
-        <v>124</v>
-      </c>
-      <c r="G94" t="s">
-        <v>14</v>
-      </c>
-      <c r="H94" t="s">
-        <v>15</v>
-      </c>
-      <c r="I94" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G94" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I94" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <v>94</v>
       </c>
@@ -3844,57 +3850,57 @@
         <v>9</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F95" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I95" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="G95" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H95" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I95" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A96">
+    </row>
+    <row r="96" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="2">
         <v>95</v>
       </c>
-      <c r="B96" t="s">
-        <v>9</v>
-      </c>
-      <c r="C96" t="s">
-        <v>106</v>
-      </c>
-      <c r="D96" t="s">
+      <c r="B96" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D96" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="E96" t="s">
-        <v>12</v>
-      </c>
-      <c r="F96" t="s">
+      <c r="E96" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F96" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="G96" t="s">
-        <v>14</v>
-      </c>
-      <c r="H96" t="s">
-        <v>15</v>
-      </c>
-      <c r="I96" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G96" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I96" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>96</v>
       </c>
@@ -3902,7 +3908,7 @@
         <v>9</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>126</v>
@@ -3920,39 +3926,39 @@
         <v>15</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A98">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="2">
         <v>97</v>
       </c>
-      <c r="B98" t="s">
-        <v>9</v>
-      </c>
-      <c r="C98" t="s">
-        <v>106</v>
-      </c>
-      <c r="D98" t="s">
+      <c r="B98" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D98" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="E98" t="s">
-        <v>12</v>
-      </c>
-      <c r="F98" t="s">
+      <c r="E98" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F98" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="G98" t="s">
-        <v>14</v>
-      </c>
-      <c r="H98" t="s">
-        <v>15</v>
-      </c>
-      <c r="I98" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G98" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I98" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
         <v>98</v>
       </c>
@@ -3960,7 +3966,7 @@
         <v>9</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>126</v>
@@ -3978,39 +3984,39 @@
         <v>15</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A100">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="2">
         <v>99</v>
       </c>
-      <c r="B100" t="s">
-        <v>9</v>
-      </c>
-      <c r="C100" t="s">
-        <v>106</v>
-      </c>
-      <c r="D100" t="s">
+      <c r="B100" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D100" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="E100" t="s">
-        <v>12</v>
-      </c>
-      <c r="F100" t="s">
+      <c r="E100" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F100" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="G100" t="s">
-        <v>14</v>
-      </c>
-      <c r="H100" t="s">
-        <v>15</v>
-      </c>
-      <c r="I100" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G100" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I100" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
         <v>100</v>
       </c>
@@ -4018,7 +4024,7 @@
         <v>9</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>126</v>
@@ -4036,39 +4042,39 @@
         <v>15</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A102">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="2">
         <v>101</v>
       </c>
-      <c r="B102" t="s">
-        <v>9</v>
-      </c>
-      <c r="C102" t="s">
-        <v>106</v>
-      </c>
-      <c r="D102" t="s">
+      <c r="B102" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D102" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="E102" t="s">
-        <v>12</v>
-      </c>
-      <c r="F102" t="s">
+      <c r="E102" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F102" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="G102" t="s">
-        <v>14</v>
-      </c>
-      <c r="H102" t="s">
-        <v>15</v>
-      </c>
-      <c r="I102" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G102" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I102" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
         <v>102</v>
       </c>
@@ -4076,7 +4082,7 @@
         <v>9</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>126</v>
@@ -4094,39 +4100,39 @@
         <v>15</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A104">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="2">
         <v>103</v>
       </c>
-      <c r="B104" t="s">
-        <v>9</v>
-      </c>
-      <c r="C104" t="s">
-        <v>106</v>
-      </c>
-      <c r="D104" t="s">
+      <c r="B104" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D104" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="E104" t="s">
-        <v>12</v>
-      </c>
-      <c r="F104" t="s">
+      <c r="E104" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F104" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="G104" t="s">
-        <v>14</v>
-      </c>
-      <c r="H104" t="s">
-        <v>15</v>
-      </c>
-      <c r="I104" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G104" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I104" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
         <v>104</v>
       </c>
@@ -4134,7 +4140,7 @@
         <v>9</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>136</v>
@@ -4152,39 +4158,39 @@
         <v>15</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A106">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="2">
         <v>105</v>
       </c>
-      <c r="B106" t="s">
-        <v>9</v>
-      </c>
-      <c r="C106" t="s">
-        <v>106</v>
-      </c>
-      <c r="D106" t="s">
+      <c r="B106" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D106" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="E106" t="s">
-        <v>12</v>
-      </c>
-      <c r="F106" t="s">
+      <c r="E106" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F106" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="G106" t="s">
-        <v>14</v>
-      </c>
-      <c r="H106" t="s">
-        <v>15</v>
-      </c>
-      <c r="I106" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G106" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I106" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
         <v>106</v>
       </c>
@@ -4192,7 +4198,7 @@
         <v>9</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>136</v>
@@ -4210,39 +4216,39 @@
         <v>15</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A108">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="2">
         <v>107</v>
       </c>
-      <c r="B108" t="s">
-        <v>9</v>
-      </c>
-      <c r="C108" t="s">
-        <v>106</v>
-      </c>
-      <c r="D108" t="s">
+      <c r="B108" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D108" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="E108" t="s">
-        <v>12</v>
-      </c>
-      <c r="F108" t="s">
+      <c r="E108" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F108" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="G108" t="s">
-        <v>14</v>
-      </c>
-      <c r="H108" t="s">
-        <v>15</v>
-      </c>
-      <c r="I108" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G108" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I108" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
         <v>108</v>
       </c>
@@ -4250,7 +4256,7 @@
         <v>9</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>141</v>
@@ -4268,39 +4274,39 @@
         <v>15</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A110">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="2">
         <v>109</v>
       </c>
-      <c r="B110" t="s">
-        <v>9</v>
-      </c>
-      <c r="C110" t="s">
-        <v>106</v>
-      </c>
-      <c r="D110" t="s">
+      <c r="B110" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D110" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="E110" t="s">
-        <v>12</v>
-      </c>
-      <c r="F110" t="s">
+      <c r="E110" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F110" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="G110" t="s">
-        <v>14</v>
-      </c>
-      <c r="H110" t="s">
-        <v>15</v>
-      </c>
-      <c r="I110" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G110" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I110" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
         <v>110</v>
       </c>
@@ -4308,7 +4314,7 @@
         <v>9</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>141</v>
@@ -4326,39 +4332,39 @@
         <v>15</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A112">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="2">
         <v>111</v>
       </c>
-      <c r="B112" t="s">
-        <v>9</v>
-      </c>
-      <c r="C112" t="s">
-        <v>106</v>
-      </c>
-      <c r="D112" t="s">
+      <c r="B112" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D112" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="E112" t="s">
-        <v>12</v>
-      </c>
-      <c r="F112" t="s">
+      <c r="E112" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F112" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="G112" t="s">
-        <v>14</v>
-      </c>
-      <c r="H112" t="s">
-        <v>15</v>
-      </c>
-      <c r="I112" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G112" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I112" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2">
         <v>112</v>
       </c>
@@ -4366,7 +4372,7 @@
         <v>9</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>146</v>
@@ -4384,39 +4390,39 @@
         <v>15</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A114">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="2">
         <v>113</v>
       </c>
-      <c r="B114" t="s">
-        <v>9</v>
-      </c>
-      <c r="C114" t="s">
-        <v>106</v>
-      </c>
-      <c r="D114" t="s">
+      <c r="B114" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D114" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="E114" t="s">
-        <v>12</v>
-      </c>
-      <c r="F114" t="s">
+      <c r="E114" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F114" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="G114" t="s">
-        <v>14</v>
-      </c>
-      <c r="H114" t="s">
-        <v>15</v>
-      </c>
-      <c r="I114" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G114" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I114" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
         <v>114</v>
       </c>
@@ -4442,39 +4448,39 @@
         <v>15</v>
       </c>
       <c r="I115" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A116">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="2">
         <v>115</v>
       </c>
-      <c r="B116" t="s">
-        <v>9</v>
-      </c>
-      <c r="C116" t="s">
+      <c r="B116" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C116" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="D116" t="s">
+      <c r="D116" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="E116" t="s">
-        <v>12</v>
-      </c>
-      <c r="F116" t="s">
+      <c r="E116" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F116" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="G116" t="s">
-        <v>14</v>
-      </c>
-      <c r="H116" t="s">
-        <v>15</v>
-      </c>
-      <c r="I116" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G116" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I116" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
         <v>116</v>
       </c>
@@ -4500,39 +4506,39 @@
         <v>15</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A118">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="2">
         <v>117</v>
       </c>
-      <c r="B118" t="s">
-        <v>9</v>
-      </c>
-      <c r="C118" t="s">
+      <c r="B118" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C118" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="D118" t="s">
+      <c r="D118" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="E118" t="s">
-        <v>12</v>
-      </c>
-      <c r="F118" t="s">
+      <c r="E118" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F118" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="G118" t="s">
-        <v>14</v>
-      </c>
-      <c r="H118" t="s">
-        <v>15</v>
-      </c>
-      <c r="I118" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G118" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I118" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
         <v>118</v>
       </c>
@@ -4558,39 +4564,39 @@
         <v>15</v>
       </c>
       <c r="I119" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A120">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="2">
         <v>119</v>
       </c>
-      <c r="B120" t="s">
-        <v>9</v>
-      </c>
-      <c r="C120" t="s">
+      <c r="B120" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C120" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="D120" t="s">
+      <c r="D120" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="E120" t="s">
-        <v>12</v>
-      </c>
-      <c r="F120" t="s">
+      <c r="E120" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F120" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="G120" t="s">
-        <v>14</v>
-      </c>
-      <c r="H120" t="s">
-        <v>15</v>
-      </c>
-      <c r="I120" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G120" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I120" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
         <v>120</v>
       </c>
@@ -4616,39 +4622,39 @@
         <v>15</v>
       </c>
       <c r="I121" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A122">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="2">
         <v>121</v>
       </c>
-      <c r="B122" t="s">
-        <v>9</v>
-      </c>
-      <c r="C122" t="s">
+      <c r="B122" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C122" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="D122" t="s">
+      <c r="D122" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="E122" t="s">
-        <v>12</v>
-      </c>
-      <c r="F122" t="s">
+      <c r="E122" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F122" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="G122" t="s">
-        <v>14</v>
-      </c>
-      <c r="H122" t="s">
-        <v>15</v>
-      </c>
-      <c r="I122" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G122" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I122" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
         <v>122</v>
       </c>
@@ -4674,39 +4680,39 @@
         <v>15</v>
       </c>
       <c r="I123" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A124">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="2">
         <v>123</v>
       </c>
-      <c r="B124" t="s">
-        <v>9</v>
-      </c>
-      <c r="C124" t="s">
+      <c r="B124" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C124" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="D124" t="s">
+      <c r="D124" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="E124" t="s">
-        <v>12</v>
-      </c>
-      <c r="F124" t="s">
+      <c r="E124" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F124" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="G124" t="s">
-        <v>14</v>
-      </c>
-      <c r="H124" t="s">
-        <v>15</v>
-      </c>
-      <c r="I124" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G124" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I124" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
         <v>124</v>
       </c>
@@ -4732,39 +4738,39 @@
         <v>15</v>
       </c>
       <c r="I125" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A126">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="2">
         <v>125</v>
       </c>
-      <c r="B126" t="s">
-        <v>9</v>
-      </c>
-      <c r="C126" t="s">
+      <c r="B126" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C126" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="D126" t="s">
+      <c r="D126" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="E126" t="s">
-        <v>12</v>
-      </c>
-      <c r="F126" t="s">
+      <c r="E126" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F126" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="G126" t="s">
-        <v>14</v>
-      </c>
-      <c r="H126" t="s">
-        <v>15</v>
-      </c>
-      <c r="I126" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G126" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I126" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
         <v>126</v>
       </c>
@@ -4790,39 +4796,39 @@
         <v>15</v>
       </c>
       <c r="I127" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A128">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="2">
         <v>127</v>
       </c>
-      <c r="B128" t="s">
-        <v>9</v>
-      </c>
-      <c r="C128" t="s">
+      <c r="B128" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C128" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="D128" t="s">
+      <c r="D128" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="E128" t="s">
-        <v>12</v>
-      </c>
-      <c r="F128" t="s">
+      <c r="E128" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F128" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="G128" t="s">
-        <v>14</v>
-      </c>
-      <c r="H128" t="s">
-        <v>15</v>
-      </c>
-      <c r="I128" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G128" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I128" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
         <v>128</v>
       </c>
@@ -4848,39 +4854,39 @@
         <v>15</v>
       </c>
       <c r="I129" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A130">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="2">
         <v>129</v>
       </c>
-      <c r="B130" t="s">
-        <v>9</v>
-      </c>
-      <c r="C130" t="s">
+      <c r="B130" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C130" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="D130" t="s">
+      <c r="D130" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="E130" t="s">
-        <v>12</v>
-      </c>
-      <c r="F130" t="s">
+      <c r="E130" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F130" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="G130" t="s">
-        <v>14</v>
-      </c>
-      <c r="H130" t="s">
-        <v>15</v>
-      </c>
-      <c r="I130" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G130" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I130" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2">
         <v>130</v>
       </c>
@@ -4906,39 +4912,39 @@
         <v>15</v>
       </c>
       <c r="I131" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A132">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="2">
         <v>131</v>
       </c>
-      <c r="B132" t="s">
-        <v>9</v>
-      </c>
-      <c r="C132" t="s">
+      <c r="B132" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C132" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="D132" t="s">
+      <c r="D132" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="E132" t="s">
-        <v>12</v>
-      </c>
-      <c r="F132" t="s">
+      <c r="E132" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F132" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="G132" t="s">
-        <v>14</v>
-      </c>
-      <c r="H132" t="s">
-        <v>15</v>
-      </c>
-      <c r="I132" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G132" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I132" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2">
         <v>132</v>
       </c>
@@ -4964,39 +4970,39 @@
         <v>15</v>
       </c>
       <c r="I133" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A134">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A134" s="2">
         <v>133</v>
       </c>
-      <c r="B134" t="s">
-        <v>9</v>
-      </c>
-      <c r="C134" t="s">
+      <c r="B134" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C134" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="D134" t="s">
+      <c r="D134" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="E134" t="s">
-        <v>12</v>
-      </c>
-      <c r="F134" t="s">
+      <c r="E134" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F134" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="G134" t="s">
-        <v>14</v>
-      </c>
-      <c r="H134" t="s">
-        <v>15</v>
-      </c>
-      <c r="I134" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G134" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I134" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2">
         <v>134</v>
       </c>
@@ -5022,39 +5028,39 @@
         <v>15</v>
       </c>
       <c r="I135" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A136">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="2">
         <v>135</v>
       </c>
-      <c r="B136" t="s">
-        <v>9</v>
-      </c>
-      <c r="C136" t="s">
+      <c r="B136" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C136" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="D136" t="s">
+      <c r="D136" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="E136" t="s">
-        <v>12</v>
-      </c>
-      <c r="F136" t="s">
+      <c r="E136" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F136" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="G136" t="s">
-        <v>14</v>
-      </c>
-      <c r="H136" t="s">
-        <v>15</v>
-      </c>
-      <c r="I136" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G136" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I136" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2">
         <v>136</v>
       </c>
@@ -5080,39 +5086,39 @@
         <v>15</v>
       </c>
       <c r="I137" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A138">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="2">
         <v>137</v>
       </c>
-      <c r="B138" t="s">
-        <v>9</v>
-      </c>
-      <c r="C138" t="s">
+      <c r="B138" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C138" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="D138" t="s">
+      <c r="D138" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="E138" t="s">
-        <v>12</v>
-      </c>
-      <c r="F138" t="s">
+      <c r="E138" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F138" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="G138" t="s">
-        <v>14</v>
-      </c>
-      <c r="H138" t="s">
-        <v>15</v>
-      </c>
-      <c r="I138" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G138" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I138" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2">
         <v>138</v>
       </c>
@@ -5141,36 +5147,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A140">
+    <row r="140" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="2">
         <v>139</v>
       </c>
-      <c r="B140" t="s">
-        <v>9</v>
-      </c>
-      <c r="C140" t="s">
+      <c r="B140" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C140" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="D140" t="s">
+      <c r="D140" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="E140" t="s">
-        <v>12</v>
-      </c>
-      <c r="F140" t="s">
+      <c r="E140" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F140" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="G140" t="s">
-        <v>14</v>
-      </c>
-      <c r="H140" t="s">
-        <v>15</v>
-      </c>
-      <c r="I140" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G140" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I140" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
         <v>140</v>
       </c>
@@ -5199,36 +5205,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A142">
+    <row r="142" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A142" s="2">
         <v>141</v>
       </c>
-      <c r="B142" t="s">
-        <v>9</v>
-      </c>
-      <c r="C142" t="s">
+      <c r="B142" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C142" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="D142" t="s">
+      <c r="D142" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="E142" t="s">
-        <v>12</v>
-      </c>
-      <c r="F142" t="s">
+      <c r="E142" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F142" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="G142" t="s">
-        <v>14</v>
-      </c>
-      <c r="H142" t="s">
-        <v>15</v>
-      </c>
-      <c r="I142" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G142" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H142" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I142" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A143" s="2">
         <v>142</v>
       </c>
@@ -5257,36 +5263,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A144">
+    <row r="144" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="2">
         <v>143</v>
       </c>
-      <c r="B144" t="s">
-        <v>9</v>
-      </c>
-      <c r="C144" t="s">
+      <c r="B144" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C144" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="D144" t="s">
+      <c r="D144" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="E144" t="s">
-        <v>12</v>
-      </c>
-      <c r="F144" t="s">
+      <c r="E144" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F144" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="G144" t="s">
-        <v>14</v>
-      </c>
-      <c r="H144" t="s">
-        <v>15</v>
-      </c>
-      <c r="I144" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G144" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H144" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I144" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2">
         <v>144</v>
       </c>
@@ -5315,36 +5321,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A146">
+    <row r="146" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="2">
         <v>145</v>
       </c>
-      <c r="B146" t="s">
-        <v>9</v>
-      </c>
-      <c r="C146" t="s">
+      <c r="B146" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C146" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="D146" t="s">
+      <c r="D146" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="E146" t="s">
-        <v>12</v>
-      </c>
-      <c r="F146" t="s">
+      <c r="E146" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F146" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="G146" t="s">
-        <v>14</v>
-      </c>
-      <c r="H146" t="s">
-        <v>15</v>
-      </c>
-      <c r="I146" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G146" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H146" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I146" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A147" s="2">
         <v>146</v>
       </c>
@@ -5373,36 +5379,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A148">
+    <row r="148" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="2">
         <v>147</v>
       </c>
-      <c r="B148" t="s">
-        <v>9</v>
-      </c>
-      <c r="C148" t="s">
+      <c r="B148" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C148" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="D148" t="s">
+      <c r="D148" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="E148" t="s">
-        <v>12</v>
-      </c>
-      <c r="F148" t="s">
+      <c r="E148" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F148" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="G148" t="s">
-        <v>14</v>
-      </c>
-      <c r="H148" t="s">
-        <v>15</v>
-      </c>
-      <c r="I148" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G148" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H148" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I148" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2">
         <v>148</v>
       </c>
@@ -5431,36 +5437,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A150">
+    <row r="150" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A150" s="2">
         <v>149</v>
       </c>
-      <c r="B150" t="s">
-        <v>9</v>
-      </c>
-      <c r="C150" t="s">
+      <c r="B150" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C150" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="D150" t="s">
+      <c r="D150" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="E150" t="s">
-        <v>12</v>
-      </c>
-      <c r="F150" t="s">
+      <c r="E150" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F150" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="G150" t="s">
-        <v>14</v>
-      </c>
-      <c r="H150" t="s">
-        <v>15</v>
-      </c>
-      <c r="I150" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G150" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H150" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I150" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A151" s="2">
         <v>150</v>
       </c>
@@ -5489,36 +5495,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A152">
+    <row r="152" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="2">
         <v>151</v>
       </c>
-      <c r="B152" t="s">
-        <v>9</v>
-      </c>
-      <c r="C152" t="s">
+      <c r="B152" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C152" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="D152" t="s">
+      <c r="D152" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="E152" t="s">
-        <v>12</v>
-      </c>
-      <c r="F152" t="s">
+      <c r="E152" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F152" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="G152" t="s">
-        <v>14</v>
-      </c>
-      <c r="H152" t="s">
-        <v>15</v>
-      </c>
-      <c r="I152" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G152" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H152" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I152" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2">
         <v>152</v>
       </c>
@@ -5547,36 +5553,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A154">
+    <row r="154" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A154" s="2">
         <v>153</v>
       </c>
-      <c r="B154" t="s">
-        <v>9</v>
-      </c>
-      <c r="C154" t="s">
+      <c r="B154" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C154" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="D154" t="s">
+      <c r="D154" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="E154" t="s">
-        <v>12</v>
-      </c>
-      <c r="F154" t="s">
+      <c r="E154" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F154" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="G154" t="s">
-        <v>14</v>
-      </c>
-      <c r="H154" t="s">
-        <v>15</v>
-      </c>
-      <c r="I154" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G154" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H154" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I154" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A155" s="2">
         <v>154</v>
       </c>
@@ -5605,36 +5611,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A156">
+    <row r="156" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A156" s="2">
         <v>155</v>
       </c>
-      <c r="B156" t="s">
-        <v>9</v>
-      </c>
-      <c r="C156" t="s">
+      <c r="B156" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C156" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="D156" t="s">
+      <c r="D156" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="E156" t="s">
-        <v>12</v>
-      </c>
-      <c r="F156" t="s">
+      <c r="E156" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F156" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="G156" t="s">
-        <v>14</v>
-      </c>
-      <c r="H156" t="s">
-        <v>15</v>
-      </c>
-      <c r="I156" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G156" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H156" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I156" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A157" s="2">
         <v>156</v>
       </c>
@@ -5663,36 +5669,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A158">
+    <row r="158" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A158" s="2">
         <v>157</v>
       </c>
-      <c r="B158" t="s">
-        <v>9</v>
-      </c>
-      <c r="C158" t="s">
+      <c r="B158" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C158" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="D158" t="s">
+      <c r="D158" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="E158" t="s">
-        <v>12</v>
-      </c>
-      <c r="F158" t="s">
+      <c r="E158" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F158" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="G158" t="s">
-        <v>14</v>
-      </c>
-      <c r="H158" t="s">
-        <v>15</v>
-      </c>
-      <c r="I158" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G158" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H158" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I158" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A159" s="2">
         <v>158</v>
       </c>
@@ -5718,39 +5724,39 @@
         <v>15</v>
       </c>
       <c r="I159" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A160">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A160" s="2">
         <v>159</v>
       </c>
-      <c r="B160" t="s">
-        <v>9</v>
-      </c>
-      <c r="C160" t="s">
+      <c r="B160" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C160" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="D160" t="s">
+      <c r="D160" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="E160" t="s">
-        <v>12</v>
-      </c>
-      <c r="F160" t="s">
+      <c r="E160" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F160" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="G160" t="s">
-        <v>14</v>
-      </c>
-      <c r="H160" t="s">
-        <v>15</v>
-      </c>
-      <c r="I160" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G160" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H160" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I160" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A161" s="2">
         <v>160</v>
       </c>
@@ -5776,39 +5782,39 @@
         <v>15</v>
       </c>
       <c r="I161" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A162">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A162" s="2">
         <v>161</v>
       </c>
-      <c r="B162" t="s">
-        <v>9</v>
-      </c>
-      <c r="C162" t="s">
+      <c r="B162" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C162" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="D162" t="s">
+      <c r="D162" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="E162" t="s">
-        <v>12</v>
-      </c>
-      <c r="F162" t="s">
+      <c r="E162" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F162" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="G162" t="s">
-        <v>14</v>
-      </c>
-      <c r="H162" t="s">
-        <v>15</v>
-      </c>
-      <c r="I162" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G162" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H162" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I162" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2">
         <v>162</v>
       </c>
@@ -5834,39 +5840,39 @@
         <v>15</v>
       </c>
       <c r="I163" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A164">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A164" s="2">
         <v>163</v>
       </c>
-      <c r="B164" t="s">
-        <v>9</v>
-      </c>
-      <c r="C164" t="s">
+      <c r="B164" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C164" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="D164" t="s">
+      <c r="D164" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="E164" t="s">
-        <v>12</v>
-      </c>
-      <c r="F164" t="s">
+      <c r="E164" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F164" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="G164" t="s">
-        <v>14</v>
-      </c>
-      <c r="H164" t="s">
-        <v>15</v>
-      </c>
-      <c r="I164" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G164" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H164" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I164" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A165" s="2">
         <v>164</v>
       </c>
@@ -5892,39 +5898,39 @@
         <v>15</v>
       </c>
       <c r="I165" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A166">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A166" s="2">
         <v>165</v>
       </c>
-      <c r="B166" t="s">
-        <v>9</v>
-      </c>
-      <c r="C166" t="s">
+      <c r="B166" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C166" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="D166" t="s">
+      <c r="D166" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="E166" t="s">
-        <v>12</v>
-      </c>
-      <c r="F166" t="s">
+      <c r="E166" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F166" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="G166" t="s">
-        <v>14</v>
-      </c>
-      <c r="H166" t="s">
-        <v>15</v>
-      </c>
-      <c r="I166" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G166" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H166" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I166" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2">
         <v>166</v>
       </c>
@@ -5950,39 +5956,39 @@
         <v>15</v>
       </c>
       <c r="I167" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A168">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A168" s="2">
         <v>167</v>
       </c>
-      <c r="B168" t="s">
-        <v>9</v>
-      </c>
-      <c r="C168" t="s">
+      <c r="B168" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C168" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="D168" t="s">
+      <c r="D168" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="E168" t="s">
-        <v>12</v>
-      </c>
-      <c r="F168" t="s">
+      <c r="E168" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F168" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="G168" t="s">
-        <v>14</v>
-      </c>
-      <c r="H168" t="s">
-        <v>15</v>
-      </c>
-      <c r="I168" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G168" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H168" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I168" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A169" s="2">
         <v>168</v>
       </c>
@@ -6008,39 +6014,39 @@
         <v>15</v>
       </c>
       <c r="I169" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A170">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A170" s="2">
         <v>169</v>
       </c>
-      <c r="B170" t="s">
-        <v>9</v>
-      </c>
-      <c r="C170" t="s">
+      <c r="B170" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C170" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="D170" t="s">
+      <c r="D170" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="E170" t="s">
-        <v>12</v>
-      </c>
-      <c r="F170" t="s">
+      <c r="E170" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F170" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="G170" t="s">
-        <v>14</v>
-      </c>
-      <c r="H170" t="s">
-        <v>15</v>
-      </c>
-      <c r="I170" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G170" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H170" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I170" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A171" s="2">
         <v>170</v>
       </c>
@@ -6066,39 +6072,39 @@
         <v>15</v>
       </c>
       <c r="I171" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A172">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A172" s="2">
         <v>171</v>
       </c>
-      <c r="B172" t="s">
-        <v>9</v>
-      </c>
-      <c r="C172" t="s">
+      <c r="B172" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C172" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="D172" t="s">
+      <c r="D172" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="E172" t="s">
-        <v>12</v>
-      </c>
-      <c r="F172" t="s">
+      <c r="E172" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F172" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="G172" t="s">
-        <v>14</v>
-      </c>
-      <c r="H172" t="s">
-        <v>15</v>
-      </c>
-      <c r="I172" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G172" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H172" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I172" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2">
         <v>172</v>
       </c>
@@ -6124,39 +6130,39 @@
         <v>15</v>
       </c>
       <c r="I173" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A174">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A174" s="2">
         <v>173</v>
       </c>
-      <c r="B174" t="s">
-        <v>9</v>
-      </c>
-      <c r="C174" t="s">
+      <c r="B174" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C174" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="D174" t="s">
+      <c r="D174" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="E174" t="s">
-        <v>12</v>
-      </c>
-      <c r="F174" t="s">
+      <c r="E174" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F174" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="G174" t="s">
-        <v>14</v>
-      </c>
-      <c r="H174" t="s">
-        <v>15</v>
-      </c>
-      <c r="I174" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G174" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H174" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I174" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A175" s="2">
         <v>174</v>
       </c>
@@ -6182,40 +6188,40 @@
         <v>15</v>
       </c>
       <c r="I175" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A176">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A176" s="2">
         <v>175</v>
       </c>
-      <c r="B176" t="s">
-        <v>9</v>
-      </c>
-      <c r="C176" t="s">
+      <c r="B176" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C176" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="D176" t="s">
+      <c r="D176" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="E176" t="s">
-        <v>12</v>
-      </c>
-      <c r="F176" t="s">
+      <c r="E176" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F176" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="G176" t="s">
-        <v>14</v>
-      </c>
-      <c r="H176" t="s">
-        <v>15</v>
-      </c>
-      <c r="I176" t="s">
-        <v>39</v>
+      <c r="G176" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H176" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I176" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1"/>
+  <autoFilter ref="A1:I176"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -6223,16 +6229,27 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="56" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="1" max="1" width="54" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>217</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -6251,11 +6268,21 @@
         <v>175</v>
       </c>
     </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+    </row>
     <row r="6" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="B6" s="4"/>
+      <c r="B6" s="4" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -6281,11 +6308,21 @@
         <v>62</v>
       </c>
     </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+    </row>
     <row r="11" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="B11" s="4"/>
+      <c r="B11" s="4" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -6297,7 +6334,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B13">
         <v>2</v>
@@ -6311,11 +6348,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>227</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>228</v>
+      </c>
+      <c r="B17">
         <v>8</v>
       </c>
     </row>
